--- a/data/LAMIS_Packing_Slip.xlsx
+++ b/data/LAMIS_Packing_Slip.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lightriver-my.sharepoint.com/personal/zsimino_lightriver_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZackerySimino\Downloads\LAMIS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{FF84441A-6DD2-4A05-A8C3-45511AF348E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85CF664-B1B3-4FD3-895E-E083F36E12D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2164AE18-DCD7-4A5D-9994-872FE7957B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="2385" windowWidth="28800" windowHeight="11295" xr2:uid="{F5EB3443-5D97-4FB8-8F2C-758476CC71EC}"/>
+    <workbookView xWindow="3690" yWindow="2055" windowWidth="28800" windowHeight="11295" activeTab="1" xr2:uid="{F5EB3443-5D97-4FB8-8F2C-758476CC71EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Packing Slip</t>
   </si>
@@ -81,12 +81,6 @@
     <t>Asset Tag</t>
   </si>
   <si>
-    <t>(Power Type) • Ambient (temp)• Software: (Software Version)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shelf: (Shelf Type)  • Part Number: (Shelf Part Number)  • Serial Number: (Shelf Serial Number) • Asset Tag: (Shelf Asset Tag) </t>
-  </si>
-  <si>
     <t>Device Summary</t>
   </si>
   <si>
@@ -100,6 +94,11 @@
   </si>
   <si>
     <t>Device ID</t>
+  </si>
+  <si>
+    <t>Lightriver Technologies 
+631 International Pkwy 
+Richardson, TX 75081, USA</t>
   </si>
 </sst>
 </file>
@@ -607,104 +606,104 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1091,1004 +1090,1004 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:9" ht="14.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="27"/>
+    </row>
+    <row r="4" spans="2:9" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="30"/>
+    </row>
+    <row r="5" spans="2:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="32"/>
+      <c r="D5" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="37"/>
-    </row>
-    <row r="3" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="38"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="40"/>
-    </row>
-    <row r="4" spans="2:9" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="41"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="43"/>
-    </row>
-    <row r="5" spans="2:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="44" t="s">
+      <c r="E5" s="31"/>
+      <c r="F5" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="44" t="s">
+      <c r="G5" s="31"/>
+      <c r="H5" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="44"/>
+      <c r="I5" s="31"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="49"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="51"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="50"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="51"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="50"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="51"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="51"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="50"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="51"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="51"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="51"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="50"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="51"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="50"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="51"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="51"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="19"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="50"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="51"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="19"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="50"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="51"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="50"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="51"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="19"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="50"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="51"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="19"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="50"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="51"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="51"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="51"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="51"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="19"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="51"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="19"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="50"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="51"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="19"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="50"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="51"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="19"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="51"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="19"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="50"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="51"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="51"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="19"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="50"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="51"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="51"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="19"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="50"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="51"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="19"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="50"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="51"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="19"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="50"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="19"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="50"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="51"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="50"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="51"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="19"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="50"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="51"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="19"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="50"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="51"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="19"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="50"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="51"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="19"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="50"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="51"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="19"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B43" s="50"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="51"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="19"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="50"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="51"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="19"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="50"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="50"/>
-      <c r="I45" s="51"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="19"/>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="50"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="50"/>
-      <c r="I46" s="51"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="19"/>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="50"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="50"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="50"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="50"/>
-      <c r="I47" s="51"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="19"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="50"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="51"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="19"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B49" s="50"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="51"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="19"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="50"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="50"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="51"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="19"/>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="50"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="50"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="50"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="50"/>
-      <c r="I51" s="51"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="19"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="50"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="50"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="51"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="19"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="50"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="50"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="50"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="50"/>
-      <c r="I53" s="51"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="19"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="50"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="50"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="50"/>
-      <c r="G54" s="51"/>
-      <c r="H54" s="50"/>
-      <c r="I54" s="51"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="19"/>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B55" s="50"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="50"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="50"/>
-      <c r="I55" s="51"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="19"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="50"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="51"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="19"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="50"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="51"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="19"/>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B58" s="50"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="50"/>
-      <c r="I58" s="51"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="19"/>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="50"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="50"/>
-      <c r="I59" s="51"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="19"/>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B60" s="50"/>
-      <c r="C60" s="51"/>
-      <c r="D60" s="50"/>
-      <c r="E60" s="51"/>
-      <c r="F60" s="50"/>
-      <c r="G60" s="51"/>
-      <c r="H60" s="50"/>
-      <c r="I60" s="51"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="19"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B61" s="50"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="50"/>
-      <c r="E61" s="51"/>
-      <c r="F61" s="50"/>
-      <c r="G61" s="51"/>
-      <c r="H61" s="50"/>
-      <c r="I61" s="51"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="19"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="50"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="50"/>
-      <c r="E62" s="51"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="50"/>
-      <c r="I62" s="51"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="19"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B63" s="50"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="50"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="50"/>
-      <c r="I63" s="51"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="19"/>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B64" s="50"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="50"/>
-      <c r="E64" s="51"/>
-      <c r="F64" s="50"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="50"/>
-      <c r="I64" s="51"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="19"/>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B65" s="50"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="50"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="50"/>
-      <c r="I65" s="51"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="19"/>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B66" s="50"/>
-      <c r="C66" s="51"/>
-      <c r="D66" s="50"/>
-      <c r="E66" s="51"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="50"/>
-      <c r="I66" s="51"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="19"/>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B67" s="50"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="50"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="50"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="50"/>
-      <c r="I67" s="51"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="19"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B68" s="50"/>
-      <c r="C68" s="51"/>
-      <c r="D68" s="50"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="50"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="50"/>
-      <c r="I68" s="51"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="19"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B69" s="50"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="50"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="50"/>
-      <c r="I69" s="51"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="19"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B70" s="50"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="51"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="19"/>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B71" s="50"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="51"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="19"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B72" s="50"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="51"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="19"/>
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B73" s="50"/>
-      <c r="C73" s="51"/>
-      <c r="D73" s="50"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="51"/>
-      <c r="H73" s="50"/>
-      <c r="I73" s="51"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="19"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B74" s="50"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="50"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="50"/>
-      <c r="I74" s="51"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="19"/>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B75" s="50"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="50"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="50"/>
-      <c r="I75" s="51"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="19"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B76" s="50"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="50"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="50"/>
-      <c r="I76" s="51"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="19"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B77" s="50"/>
-      <c r="C77" s="51"/>
-      <c r="D77" s="50"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="51"/>
-      <c r="H77" s="50"/>
-      <c r="I77" s="51"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="19"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B78" s="50"/>
-      <c r="C78" s="51"/>
-      <c r="D78" s="50"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="51"/>
-      <c r="H78" s="50"/>
-      <c r="I78" s="51"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="19"/>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B79" s="50"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="50"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="51"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="18"/>
+      <c r="I79" s="19"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B80" s="50"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="51"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="51"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="19"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B81" s="50"/>
-      <c r="C81" s="51"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="51"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="19"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B82" s="50"/>
-      <c r="C82" s="51"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="51"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="51"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="19"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B83" s="50"/>
-      <c r="C83" s="51"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="50"/>
-      <c r="I83" s="51"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="19"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B84" s="50"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="50"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="50"/>
-      <c r="I84" s="51"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="19"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B85" s="50"/>
-      <c r="C85" s="51"/>
-      <c r="D85" s="50"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="50"/>
-      <c r="I85" s="51"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="19"/>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B86" s="50"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="50"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="50"/>
-      <c r="I86" s="51"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="19"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="19"/>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B87" s="50"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="50"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="50"/>
-      <c r="I87" s="51"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="19"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="19"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="19"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B88" s="50"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="50"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="50"/>
-      <c r="I88" s="51"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="19"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="19"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B89" s="50"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="50"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="51"/>
-      <c r="H89" s="50"/>
-      <c r="I89" s="51"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="19"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="19"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B90" s="50"/>
-      <c r="C90" s="51"/>
-      <c r="D90" s="50"/>
-      <c r="E90" s="51"/>
-      <c r="F90" s="50"/>
-      <c r="G90" s="51"/>
-      <c r="H90" s="50"/>
-      <c r="I90" s="51"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="18"/>
+      <c r="E90" s="19"/>
+      <c r="F90" s="18"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="18"/>
+      <c r="I90" s="19"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B91" s="50"/>
-      <c r="C91" s="51"/>
-      <c r="D91" s="50"/>
-      <c r="E91" s="51"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="51"/>
-      <c r="H91" s="50"/>
-      <c r="I91" s="51"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="19"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="19"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B92" s="50"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="50"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="51"/>
-      <c r="H92" s="50"/>
-      <c r="I92" s="51"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="19"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="19"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="19"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="19"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B93" s="50"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="50"/>
-      <c r="E93" s="51"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="51"/>
-      <c r="H93" s="50"/>
-      <c r="I93" s="51"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="19"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="19"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B94" s="50"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="50"/>
-      <c r="E94" s="51"/>
-      <c r="F94" s="50"/>
-      <c r="G94" s="51"/>
-      <c r="H94" s="50"/>
-      <c r="I94" s="51"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="19"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="19"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="19"/>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B95" s="50"/>
-      <c r="C95" s="51"/>
-      <c r="D95" s="50"/>
-      <c r="E95" s="51"/>
-      <c r="F95" s="50"/>
-      <c r="G95" s="51"/>
-      <c r="H95" s="50"/>
-      <c r="I95" s="51"/>
+      <c r="B95" s="18"/>
+      <c r="C95" s="19"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="19"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="19"/>
+      <c r="H95" s="18"/>
+      <c r="I95" s="19"/>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B96" s="50"/>
-      <c r="C96" s="51"/>
-      <c r="D96" s="50"/>
-      <c r="E96" s="51"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="51"/>
-      <c r="H96" s="50"/>
-      <c r="I96" s="51"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="19"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="19"/>
+      <c r="F96" s="18"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="18"/>
+      <c r="I96" s="19"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="50"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="50"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="50"/>
-      <c r="I97" s="51"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="18"/>
+      <c r="I97" s="19"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" s="50"/>
-      <c r="C98" s="51"/>
-      <c r="D98" s="50"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="50"/>
-      <c r="I98" s="51"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="18"/>
+      <c r="I98" s="19"/>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B99" s="50"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="50"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="50"/>
-      <c r="I99" s="51"/>
+      <c r="B99" s="18"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="18"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="19"/>
+      <c r="H99" s="18"/>
+      <c r="I99" s="19"/>
     </row>
     <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="52"/>
-      <c r="C100" s="53"/>
-      <c r="D100" s="52"/>
-      <c r="E100" s="53"/>
-      <c r="F100" s="52"/>
-      <c r="G100" s="53"/>
-      <c r="H100" s="52"/>
-      <c r="I100" s="53"/>
+      <c r="B100" s="20"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="20"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="20"/>
+      <c r="G100" s="21"/>
+      <c r="H100" s="20"/>
+      <c r="I100" s="21"/>
     </row>
     <row r="101" spans="2:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -2114,30 +2113,30 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="23"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="42"/>
     </row>
     <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="26"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
@@ -2145,11 +2144,11 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="48"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -2157,9 +2156,11 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
+      <c r="E6" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="7" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -2167,67 +2168,63 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
     </row>
     <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
     </row>
     <row r="9" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" spans="2:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
